--- a/data/trans_dic/IP12B$vomitos-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$vomitos-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por vómitos</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por vómitos (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,5</t>
+          <t>0,0; 42,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,68</t>
+          <t>0,0; 22,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,09</t>
+          <t>0,0; 24,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,94</t>
+          <t>0,0; 31,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,18</t>
+          <t>0,0; 46,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,27</t>
+          <t>0,0; 35,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,07</t>
+          <t>0,0; 23,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,01</t>
+          <t>0,0; 12,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,62</t>
+          <t>0,0; 20,44</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,54</t>
+          <t>0,0; 39,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,58</t>
+          <t>0,0; 21,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,43</t>
+          <t>0,0; 47,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,97</t>
+          <t>0,0; 25,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,36</t>
+          <t>0,0; 22,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,95</t>
+          <t>0,0; 15,95</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,52</t>
+          <t>0,0; 43,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,5</t>
+          <t>0,0; 22,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,77</t>
+          <t>0,0; 65,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,77</t>
+          <t>0,0; 55,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,01</t>
+          <t>0,0; 23,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,52</t>
+          <t>0,0; 21,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,24</t>
+          <t>0,0; 46,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,66</t>
+          <t>0,0; 20,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,51</t>
+          <t>0,0; 37,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,62</t>
+          <t>0,0; 17,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,66</t>
+          <t>0,0; 27,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,13</t>
+          <t>0,0; 11,56</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,23; 12,36</t>
+          <t>1,38; 12,56</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,1</t>
+          <t>0,0; 7,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,5</t>
+          <t>0,0; 7,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,35; 11,25</t>
+          <t>1,36; 11,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,53</t>
+          <t>1,01; 9,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,75</t>
+          <t>0,0; 7,33</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,1; 9,75</t>
+          <t>2,02; 9,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,03; 7,08</t>
+          <t>1,05; 6,35</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,71</t>
+          <t>0,54; 5,31</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por vómitos (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3356</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3092</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1255</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2565</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3846</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2685</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2835</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3866</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3169</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3519</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3161</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3317</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3073</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2468</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3263</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3113</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2763</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3384</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2654</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3361</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2735</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2841</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2683</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2840</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3931</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3362</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4670</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2757</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>1414</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1128</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>2284</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>4291</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>3698</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>607; 5510</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>0; 4823</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>0; 3944</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>637; 5211</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>642; 6073</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0; 3509</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>1827; 8285</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>1313; 7923</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>558; 5471</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$vomitos-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$vomitos-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por vómitos (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por vómitos (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,52</t>
+          <t>0,0; 38,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,7</t>
+          <t>0,0; 32,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,89</t>
+          <t>0,0; 24,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,69</t>
+          <t>0,0; 23,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,13</t>
+          <t>0,0; 45,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,22 +813,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,4</t>
+          <t>0,0; 43,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,97</t>
+          <t>0,0; 23,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,17</t>
+          <t>0,0; 12,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,44</t>
+          <t>0,0; 20,0</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,4</t>
+          <t>0,0; 57,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,68</t>
+          <t>0,0; 20,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,63</t>
+          <t>0,0; 49,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,07</t>
+          <t>0,0; 29,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,31</t>
+          <t>0,0; 22,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,95</t>
+          <t>0,0; 14,29</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,39</t>
+          <t>0,0; 52,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,93</t>
+          <t>0,0; 23,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,65</t>
+          <t>0,0; 48,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,55</t>
+          <t>0,0; 23,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,53</t>
+          <t>0,0; 21,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,23</t>
+          <t>0,0; 46,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,94</t>
+          <t>0,0; 21,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,97</t>
+          <t>0,0; 40,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1478,17 +1478,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,07</t>
+          <t>0,0; 17,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,1</t>
+          <t>0,0; 25,49</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,56</t>
+          <t>0,0; 13,55</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,38; 12,56</t>
+          <t>1,45; 13,67</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,87</t>
+          <t>0,0; 9,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,15</t>
+          <t>0,0; 6,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,36; 11,16</t>
+          <t>1,37; 11,64</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,56</t>
+          <t>1,01; 10,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,33</t>
+          <t>0,0; 7,79</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,02; 9,15</t>
+          <t>2,06; 9,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,05; 6,35</t>
+          <t>1,03; 6,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,31</t>
+          <t>0,54; 4,67</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por vómitos (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por vómitos (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3356</t>
+          <t>0; 3068</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3092</t>
+          <t>0; 4391</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2565</t>
+          <t>0; 2566</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3846</t>
+          <t>0; 2840</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2685</t>
+          <t>0; 2658</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2049,22 +2049,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2835</t>
+          <t>0; 3466</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3866</t>
+          <t>0; 3834</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3169</t>
+          <t>0; 3174</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3519</t>
+          <t>0; 3444</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3161</t>
+          <t>0; 4607</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3317</t>
+          <t>0; 3171</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3073</t>
+          <t>0; 3220</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2468</t>
+          <t>0; 2943</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3263</t>
+          <t>0; 3334</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3113</t>
+          <t>0; 2789</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2763</t>
+          <t>0; 3369</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3384</t>
+          <t>0; 3405</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3361</t>
+          <t>0; 2944</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2869,12 +2869,12 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2735</t>
+          <t>0; 2680</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 2841</t>
+          <t>0; 2787</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 2683</t>
+          <t>0; 2680</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 2840</t>
+          <t>0; 2964</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 3931</t>
+          <t>0; 4217</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3032,17 +3032,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 3362</t>
+          <t>0; 3401</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 4670</t>
+          <t>0; 4392</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 2757</t>
+          <t>0; 3230</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>607; 5510</t>
+          <t>634; 5999</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 4823</t>
+          <t>0; 5561</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0; 3944</t>
+          <t>0; 3824</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>637; 5211</t>
+          <t>639; 5435</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>642; 6073</t>
+          <t>640; 6486</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0; 3509</t>
+          <t>0; 3728</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1827; 8285</t>
+          <t>1864; 8578</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1313; 7923</t>
+          <t>1286; 8131</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>558; 5471</t>
+          <t>559; 4812</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$vomitos-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$vomitos-Provincia-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,7 +625,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 38,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,24</t>
+          <t>0,0; 22,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>11,03%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8,74%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>5,94%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>5,17%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11,03%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,9</t>
+          <t>0,0; 48,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 36,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,66</t>
+          <t>0,0; 29,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 24,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,77</t>
+          <t>0,0; 26,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,19</t>
+          <t>0,0; 10,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,0</t>
+          <t>0,0; 20,62</t>
         </is>
       </c>
     </row>
@@ -850,22 +850,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>9,81%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 55,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,73</t>
+          <t>0,0; 22,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>16,23%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5,73%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 54,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 25,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,8</t>
+          <t>0,0; 26,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,29</t>
+          <t>0,0; 16,95</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 43,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,07</t>
+          <t>0,0; 18,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1285,12 +1285,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 66,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 45,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,08</t>
+          <t>0,0; 28,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,12</t>
+          <t>0,0; 25,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1395,32 +1395,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>9,58%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>11,27%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>4,16%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>9,58%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 37,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 46,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 17,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,27</t>
+          <t>0,0; 16,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,49</t>
+          <t>0,0; 27,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,55</t>
+          <t>0,0; 12,13</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>5,27%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2,31%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2,05%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,45; 13,67</t>
+          <t>1,35; 11,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,07</t>
+          <t>1,01; 9,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,94</t>
+          <t>0,0; 7,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,37; 11,64</t>
+          <t>1,23; 12,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,01; 10,21</t>
+          <t>0,0; 8,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,79</t>
+          <t>0,0; 6,5</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,06; 9,47</t>
+          <t>2,1; 9,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,03; 6,51</t>
+          <t>1,03; 7,08</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,67</t>
+          <t>0,54; 4,71</t>
         </is>
       </c>
     </row>
@@ -1660,14 +1660,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>685</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3038</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3068</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4391</t>
+          <t>0; 3089</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1923,14 +1923,14 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1971,32 +1971,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>613</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2566</t>
+          <t>0; 2804</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2840</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2904</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2658</t>
+          <t>0; 2999</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3027</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3466</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3834</t>
+          <t>0; 4205</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3174</t>
+          <t>0; 2607</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3444</t>
+          <t>0; 3552</t>
         </is>
       </c>
     </row>
@@ -2086,22 +2086,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -2139,22 +2139,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>787</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4607</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4455</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3171</t>
+          <t>0; 3456</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2244,32 +2244,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2297,32 +2297,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1047</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>564</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3220</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2943</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3511</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2556</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3334</t>
+          <t>0; 3855</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 2789</t>
+          <t>0; 3308</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>647</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2772</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3369</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3405</t>
+          <t>0; 2730</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2786,12 +2786,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>650</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>645</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2801,12 +2801,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2700</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2765</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2854,12 +2854,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 2654</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 2944</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2869,12 +2869,12 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2680</t>
+          <t>0; 3253</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 2787</t>
+          <t>0; 3369</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2896,32 +2896,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2949,32 +2949,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>654</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>564</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>992</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 2680</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3883</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 2964</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2683</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 4217</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2395</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 3401</t>
+          <t>0; 3273</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 4392</t>
+          <t>0; 4766</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 3230</t>
+          <t>0; 2893</t>
         </is>
       </c>
     </row>
@@ -3059,32 +3059,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>2284</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>2313</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1414</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>1128</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>2284</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>634; 5999</t>
+          <t>631; 5254</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 5561</t>
+          <t>644; 6058</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0; 3824</t>
+          <t>0; 3707</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>639; 5435</t>
+          <t>538; 5422</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>640; 6486</t>
+          <t>0; 4968</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0; 3728</t>
+          <t>0; 3582</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1864; 8578</t>
+          <t>1904; 8831</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1286; 8131</t>
+          <t>1284; 8837</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>559; 4812</t>
+          <t>557; 4848</t>
         </is>
       </c>
     </row>
